--- a/artfynd/A 315-2024 artfynd.xlsx
+++ b/artfynd/A 315-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>115162726</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
+        <v>56502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 315-2024 artfynd.xlsx
+++ b/artfynd/A 315-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115162726</v>
       </c>
       <c r="B2" t="n">
-        <v>56504</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 315-2024 artfynd.xlsx
+++ b/artfynd/A 315-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115162726</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 315-2024 artfynd.xlsx
+++ b/artfynd/A 315-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115162726</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 315-2024 artfynd.xlsx
+++ b/artfynd/A 315-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115162726</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 315-2024 artfynd.xlsx
+++ b/artfynd/A 315-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115162726</v>
+        <v>116012660</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 315-2024, Boh</t>
+          <t>Sollums Lång, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>327840</v>
+        <v>328052</v>
       </c>
       <c r="R2" t="n">
-        <v>6455191</v>
+        <v>6454814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vinterspillning</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116012677</v>
+        <v>116012680</v>
       </c>
       <c r="B3" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>327635</v>
+        <v>328077</v>
       </c>
       <c r="R3" t="n">
-        <v>6455001</v>
+        <v>6454824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116012665</v>
+        <v>116012702</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>328083</v>
+        <v>328044</v>
       </c>
       <c r="R4" t="n">
-        <v>6454794</v>
+        <v>6454799</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116012680</v>
+        <v>116012642</v>
       </c>
       <c r="B5" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>328077</v>
+        <v>327829</v>
       </c>
       <c r="R5" t="n">
-        <v>6454824</v>
+        <v>6454848</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116012671</v>
+        <v>116012643</v>
       </c>
       <c r="B6" t="n">
-        <v>96619</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>327863</v>
+        <v>327910</v>
       </c>
       <c r="R6" t="n">
-        <v>6454873</v>
+        <v>6454810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116012659</v>
+        <v>116012644</v>
       </c>
       <c r="B7" t="n">
-        <v>95932</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327998</v>
+        <v>327886</v>
       </c>
       <c r="R7" t="n">
-        <v>6454905</v>
+        <v>6454843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116012648</v>
+        <v>116012663</v>
       </c>
       <c r="B8" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327673</v>
+        <v>327797</v>
       </c>
       <c r="R8" t="n">
-        <v>6455021</v>
+        <v>6454831</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116012645</v>
+        <v>116012665</v>
       </c>
       <c r="B9" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>327829</v>
+        <v>328083</v>
       </c>
       <c r="R9" t="n">
-        <v>6455009</v>
+        <v>6454794</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116012685</v>
+        <v>116012694</v>
       </c>
       <c r="B10" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>327637</v>
+        <v>327915</v>
       </c>
       <c r="R10" t="n">
-        <v>6454982</v>
+        <v>6454814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,37 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116012666</v>
+        <v>116012659</v>
       </c>
       <c r="B11" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>327826</v>
+        <v>327998</v>
       </c>
       <c r="R11" t="n">
-        <v>6454962</v>
+        <v>6454905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,15 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116012695</v>
+        <v>115162758</v>
       </c>
       <c r="B12" t="n">
-        <v>80109</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,37 +1666,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollums Lång, Boh</t>
+          <t>A 315-2024, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>327879</v>
+        <v>328068</v>
       </c>
       <c r="R12" t="n">
-        <v>6454915</v>
+        <v>6454907</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1793,12 +1732,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,55 +1746,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116012663</v>
+        <v>116012677</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>327797</v>
+        <v>327635</v>
       </c>
       <c r="R13" t="n">
-        <v>6454831</v>
+        <v>6455001</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1840,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,15 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116012693</v>
+        <v>116012679</v>
       </c>
       <c r="B14" t="n">
-        <v>96839</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,21 +1878,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220686</v>
+        <v>2606</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>327809</v>
+        <v>327947</v>
       </c>
       <c r="R14" t="n">
-        <v>6454886</v>
+        <v>6454866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,15 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116012683</v>
+        <v>116012681</v>
       </c>
       <c r="B15" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>327767</v>
+        <v>327879</v>
       </c>
       <c r="R15" t="n">
-        <v>6455076</v>
+        <v>6454915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,15 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116012684</v>
+        <v>116012682</v>
       </c>
       <c r="B16" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>327737</v>
+        <v>327800</v>
       </c>
       <c r="R16" t="n">
-        <v>6455028</v>
+        <v>6455020</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,15 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116012679</v>
+        <v>116012683</v>
       </c>
       <c r="B17" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>327947</v>
+        <v>327767</v>
       </c>
       <c r="R17" t="n">
-        <v>6454866</v>
+        <v>6455076</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,15 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116012660</v>
+        <v>116012684</v>
       </c>
       <c r="B18" t="n">
-        <v>95932</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,21 +2266,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2380,10 +2290,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>328052</v>
+        <v>327737</v>
       </c>
       <c r="R18" t="n">
-        <v>6454814</v>
+        <v>6455028</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,15 +2352,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116012696</v>
+        <v>116012685</v>
       </c>
       <c r="B19" t="n">
-        <v>80109</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,21 +2363,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2482,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>327834</v>
+        <v>327637</v>
       </c>
       <c r="R19" t="n">
-        <v>6455020</v>
+        <v>6454982</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,37 +2449,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>116012664</v>
+        <v>116012645</v>
       </c>
       <c r="B20" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2584,10 +2484,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>328091</v>
+        <v>327829</v>
       </c>
       <c r="R20" t="n">
-        <v>6455076</v>
+        <v>6455009</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,11 +2520,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2651,15 +2546,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116012644</v>
+        <v>116012647</v>
       </c>
       <c r="B21" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2691,10 +2581,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>327886</v>
+        <v>327774</v>
       </c>
       <c r="R21" t="n">
-        <v>6454843</v>
+        <v>6455023</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,15 +2643,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116012647</v>
+        <v>116012648</v>
       </c>
       <c r="B22" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,10 +2678,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>327774</v>
+        <v>327673</v>
       </c>
       <c r="R22" t="n">
-        <v>6455023</v>
+        <v>6455021</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,15 +2740,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116012681</v>
+        <v>116012664</v>
       </c>
       <c r="B23" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,21 +2751,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2895,10 +2775,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>327879</v>
+        <v>328091</v>
       </c>
       <c r="R23" t="n">
-        <v>6454915</v>
+        <v>6455076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,6 +2811,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,15 +2842,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116012642</v>
+        <v>116012666</v>
       </c>
       <c r="B24" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,21 +2853,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2997,10 +2877,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>327829</v>
+        <v>327826</v>
       </c>
       <c r="R24" t="n">
-        <v>6454848</v>
+        <v>6454962</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,6 +2913,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3059,15 +2944,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116012682</v>
+        <v>115162726</v>
       </c>
       <c r="B25" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3075,34 +2955,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2606</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sollums Lång, Boh</t>
+          <t>A 315-2024, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>327800</v>
+        <v>327840</v>
       </c>
       <c r="R25" t="n">
-        <v>6455020</v>
+        <v>6455191</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,12 +3017,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Vinterspillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,27 +3042,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116012702</v>
+        <v>116012693</v>
       </c>
       <c r="B26" t="n">
-        <v>94156</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3177,21 +3065,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>220686</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3201,10 +3089,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>328044</v>
+        <v>327809</v>
       </c>
       <c r="R26" t="n">
-        <v>6454799</v>
+        <v>6454886</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3263,15 +3151,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116012694</v>
+        <v>116012671</v>
       </c>
       <c r="B27" t="n">
-        <v>80109</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3279,21 +3162,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230185</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3303,10 +3186,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>327915</v>
+        <v>327863</v>
       </c>
       <c r="R27" t="n">
-        <v>6454814</v>
+        <v>6454873</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3365,15 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116012643</v>
+        <v>116012695</v>
       </c>
       <c r="B28" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,21 +3259,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>230185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3405,10 +3283,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>327910</v>
+        <v>327879</v>
       </c>
       <c r="R28" t="n">
-        <v>6454810</v>
+        <v>6454915</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3464,6 +3342,103 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>116012696</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sollums Lång, Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>327834</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6455020</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 315-2024 artfynd.xlsx
+++ b/artfynd/A 315-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012685</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012648</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012659</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012660</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115162758</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012679</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012680</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012681</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012682</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012683</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012684</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012702</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2048,6 +2118,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012642</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012643</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012644</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012645</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012647</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2538,6 +2633,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012663</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2640,6 +2740,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012664</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2742,6 +2847,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012665</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2844,6 +2954,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012666</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2954,6 +3069,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115162726</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3051,6 +3171,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012693</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3148,6 +3273,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012671</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3245,6 +3375,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012694</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3342,6 +3477,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012695</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3439,8 +3579,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012696</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>